--- a/光伏配储项目/电价数据/2026/漱玉站.xlsx
+++ b/光伏配储项目/电价数据/2026/漱玉站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51485</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.75238</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57913</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5887899999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.52359</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.51422</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43813</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45505</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.4226</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42705</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40981</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39783</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39555</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38524</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41736</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39246</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42114</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41432</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42433</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41196</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44273</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27719</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12203</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10001</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11086</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.10274</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.12142</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04357</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.09259000000000001</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.14698</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.12917</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.10152</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09068999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.06506000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.12057</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.10287</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14666</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21392</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23491</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25212</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22242</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.13532</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.01859</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.13079</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.28294</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.27872</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.27806</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.21463</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.45439</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.50612</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.63834</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.5561799999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.44091</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44012</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42984</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5647000000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.45134</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.60766</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.8064</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.62053</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.64942</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.74879</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.99199</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.66177</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58388</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.76997</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.44613</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6248400000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6079</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5223099999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47131</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42602</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.69572</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.8178300000000001</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.59878</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.6185900000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48293</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51739</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50459</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50562</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48675</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40088</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41716</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.47675</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.53503</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.42122</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42739</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.44093</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50744</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.37397</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.40691</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.48814</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7557699999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9739800000000001</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.64835</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.81313</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.74885</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.65077</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.7231599999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.5674600000000001</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.91073</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.83949</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.42088</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37552</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.49554</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.48138</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.52337</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.9846200000000001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.64943</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.5731000000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.5799</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.5780700000000001</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.43643</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.41008</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.78254</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.5599700000000001</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.49153</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.5761499999999999</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.55706</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6751699999999999</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6036</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.72529</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.42255</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7732899999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.49883</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.44555</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43131</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40838</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33471</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51201</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.45458</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.46161</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45201</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.38384</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43139</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44732</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47366</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44748</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44175</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.21978</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27457</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.5480499999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.49424</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.03322</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.61286</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.6375299999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.49719</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.51385</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.49578</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.56292</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.64173</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.65074</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.49342</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.41881</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50544</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.41372</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.47081</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.41238</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.47176</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.57078</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.53653</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6186200000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.61363</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5884199999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.47474</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.49414</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40805</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.45861</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.44036</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.46407</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44903</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.42627</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.40531</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40157</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36411</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34213</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52561</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45317</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.39701</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26591</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.09848</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.23858</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.21592</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.23159</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30642</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5462899999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.42199</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.21622</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.49362</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.44532</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.54334</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.50152</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48592</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.26203</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30266</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.15503</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.40448</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.46395</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.39701</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32797</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38234</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04467</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.28622</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03098</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04652000000000001</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.18154</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.21997</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.20347</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15735</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04589</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04983</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04391</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03821</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04353</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21824</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05677</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.0492</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04315</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00023</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.07135</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.40274</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03999</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.10068</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29015</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29211</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39895</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40962</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46671</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39563</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39898</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35006</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36787</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.65447</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44088</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.41876</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.4182</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10255</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04352</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04566</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04397</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.7415499999999999</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.07224</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.10838</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.28911</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.44492</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.008230000000000001</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04577000000000001</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.0437</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04552</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04343</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04522</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04528</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04362</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.1791</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.0447</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04995</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04975</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04739</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04788000000000001</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.1998</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14275</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29338</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29683</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26878</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33493</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31689</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40331</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.2709</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17091</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14769</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15857</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2361</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21399</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28567</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28044</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28093</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42837</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45674</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41867</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41552</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29934</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15648</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50769</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62205</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78104</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92043</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49459</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91443</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8633500000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29659</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8881</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63174</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18769</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86883</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5268699999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33145</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03333</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53137</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7914600000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5268400000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77346</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7779199999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87683</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87412</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.4936</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39912</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40049</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45046</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20759</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87887</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55104</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6224400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5384800000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49787</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.4559</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42434</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43726</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38833</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.4527</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41983</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38496</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43281</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40063</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45057</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39798</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5828</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42479</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5945499999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5987</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.68038</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46992</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41548</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.57813</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44864</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.61638</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.88214</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.83648</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86151</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43874</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.70013</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.42789</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27737</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30304</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40731</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.44875</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41218</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.38937</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37287</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35269</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91622</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46199</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.48804</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4036</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.4581</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49533</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29051</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29297</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16864</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26246</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19886</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27705</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19174</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28967</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25552</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27635</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43612</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42299</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44827</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41807</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5889500000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88781</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.57914</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.15065</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69784</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7883</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65588</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57094</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44451</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44941</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49961</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43901</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.4351</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41411</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42137</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49606</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43325</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41007</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43336</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42461</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44647</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39549</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42275</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43063</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41228</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39755</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49265</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30304</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.09759000000000001</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.56853</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24981</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.00528</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.21312</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.23323</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.28984</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28662</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.19853</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26082</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25516</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28571</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40335</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36313</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.56841</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.80588</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46101</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43383</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.49554</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38367</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32181</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.41822</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.30909</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.27713</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.29205</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.0258</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.28827</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23499</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14957</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.15155</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28116</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15824</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14231</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14309</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14177</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25761</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14234</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26326</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26116</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.1442</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.13214</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11294</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11182</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14547</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.1424</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14797</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28655</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37739</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4451</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.39822</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39419</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44418</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43523</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43467</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.43952</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44285</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40101</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39627</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34683</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53174</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38766</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46388</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42012</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41239</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37823</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28167</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27038</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26601</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.2078</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.25232</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24447</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26949</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28865</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29723</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28883</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24197</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30695</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25564</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41284</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37774</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38321</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35866</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41346</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38698</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.39401</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39201</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43122</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42599</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.66255</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.41408</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.41262</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.79047</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.78577</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24707</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.7255199999999999</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.92814</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.60772</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.3732200000000001</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41903</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43156</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43551</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42004</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6917000000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5143300000000001</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22793</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34652</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.4643</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28316</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34884</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36722</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38308</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41151</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41073</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6564099999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.75985</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45448</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34336</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41042</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37544</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36953</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26535</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.1497</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29614</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28027</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28205</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20203</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25228</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28173</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28123</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.2191</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25995</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28573</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.2787</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.42571</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40551</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.63174</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.59333</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.59305</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46624</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7531599999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47674</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.7940499999999999</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.42733</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48585</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39677</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.46339</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42726</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35879</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.4853</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5251399999999999</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47744</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.47819</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41427</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39487</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.4076</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40558</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41367</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40795</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40617</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38804</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39698</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39679</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44463</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44409</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55071</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49328</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44539</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.50984</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44447</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46158</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37717</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41964</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.45458</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.53437</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43512</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.4067</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6631900000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.56374</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41082</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48847</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43536</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.49398</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.49919</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.53359</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.67998</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.70159</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.77467</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.4842</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.7977799999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.57866</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5229299999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.82447</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7729400000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6241</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6735</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44319</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47118</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.47912</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47289</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46631</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41479</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.54795</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42562</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4386</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.4525</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44246</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41565</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39678</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39456</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40164</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39376</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37621</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38448</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39687</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37359</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.21024</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38146</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.009650000000000001</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44536</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.45685</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11263</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18134</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41461</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43211</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41478</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41301</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38693</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40499</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40626</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37534</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39378</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39667</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37279</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36167</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.43967</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27221</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.2215</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28583</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23161</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28357</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25071</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25077</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.1347</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29117</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24428</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04212</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.24996</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28212</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17238</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18896</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27442</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30508</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23417</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25671</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26209</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23171</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27531</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28294</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28305</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.39321</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34644</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.29906</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28026</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.27798</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.18772</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24615</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.24453</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01736</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00061</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.01148</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.13401</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.00651</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.0394</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01459</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04078</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03815</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04813</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04770000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02457</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02708</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04923</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00135</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.24126</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04923</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02377</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04937</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03866</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18371</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.23865</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2684</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27987</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.29235</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.28386</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.38996</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.15847</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.2689</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.60773</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.44366</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.38183</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.29349</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.28705</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.40842</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.29148</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6824600000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.82799</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.79938</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.64932</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.26678</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.004940000000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.23623</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.21051</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.24043</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.23541</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.21999</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.25024</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.22955</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.02259</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.1782</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.20681</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.02143</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.23555</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.01045</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.23963</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.24776</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.23901</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.03166</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.21855</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.23083</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.22418</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.19958</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25591</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27484</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.41585</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32096</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.09340999999999999</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.76679</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.36851</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.51069</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5246499999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.41126</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.41025</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.43086</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.43209</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.42522</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14154</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27027</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.25556</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32617</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.47751</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.49036</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.40463</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25761</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47854</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.48314</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41698</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.49981</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.42211</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.47881</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.74551</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.3683999999999999</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41401</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45337</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.25301</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36628</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47531</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.39835</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.39796</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37474</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36733</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39586</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39852</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.44317</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37279</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.43771</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30198</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.3816000000000001</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38742</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42782</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42734</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50986</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.58224</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.59814</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.5324099999999999</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.68306</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.7190599999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49997</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5448</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.6216</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.5388500000000001</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.71148</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.95199</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.74466</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.48497</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5320199999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.49018</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44189</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39537</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37067</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3732200000000001</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37747</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.1629</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.06984</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.18779</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.21159</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.15765</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.02172</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26312</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.15945</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05472999999999999</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.07764</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.08705</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.2475</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05912</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.2042</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.18442</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38305</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.50168</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.41542</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.44209</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.43157</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39417</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42194</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38937</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.4277</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37813</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36894</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.95802</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.54186</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.47726</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.43165</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.39801</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.6882200000000001</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.02048</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.67615</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.15384</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.7277400000000001</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.5305</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.6216900000000001</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.6385700000000001</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.38811</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.40405</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40475</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37198</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38423</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.40377</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36305</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.16371</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.27243</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.28368</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.13233</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.17986</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.19556</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.4363</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04435</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.19907</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.52652</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.24511</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.18538</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.42747</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.50601</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.20573</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.23884</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.14146</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.28024</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.14201</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.61198</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.28326</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.17787</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.13389</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26332</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.22793</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.28845</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47322</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38945</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37263</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38155</v>
       </c>
     </row>
   </sheetData>
